--- a/files/telco_b2b_monitor_20260428.xlsx
+++ b/files/telco_b2b_monitor_20260428.xlsx
@@ -1090,7 +1090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G178"/>
+  <dimension ref="A1:G179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7653,6 +7653,43 @@
         </is>
       </c>
       <c r="G178" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="36" customHeight="1">
+      <c r="A179" s="19" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="19" t="inlineStr">
+        <is>
+          <t>Generale</t>
+        </is>
+      </c>
+      <c r="C179" s="20" t="inlineStr">
+        <is>
+          <t>ITU, le prossime elezioni banco di prova politico per il governo dell'AI</t>
+        </is>
+      </c>
+      <c r="D179" s="19" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E179" s="19" t="inlineStr">
+        <is>
+          <t>Alla Conferenza di Doha previsto il rinnovo dei vertici ITU. Russia e Cina vorrebbero ampliamento dei poteri su web, cybersicurezza e AI. La governance dell'intelligenza artificiale al centro del dibattito internazionale con riflessi diretti sul mercato telco.</t>
+        </is>
+      </c>
+      <c r="F179" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G179" s="19" t="inlineStr">
         <is>
           <t>🆕 Sì</t>
         </is>
@@ -7839,6 +7876,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId175"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId177"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
